--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:45</t>
+    <t xml:space="preserve">2026-09-24 00:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -727,7 +727,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G21" s="2"/>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G23" s="2"/>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G33" s="2"/>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G34" s="2"/>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G35" s="2"/>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G45" s="2"/>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G46" s="2"/>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G47" s="2"/>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G57" s="2"/>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="G59" s="2"/>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G70" s="2"/>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G71" s="2"/>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="G80" s="2"/>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="G93" s="2"/>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G95" s="2"/>
     </row>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:35</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
